--- a/data/信用债发行汇总_2026-09-08.xlsx
+++ b/data/信用债发行汇总_2026-09-08.xlsx
@@ -10564,7 +10564,11 @@
           <t>26赣建工MTN001</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>102683554.IB</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -10740,7 +10744,11 @@
           <t>26冀中峰峰MTN002B</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>102683553.IB</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -11088,7 +11096,11 @@
           <t>26冀中峰峰MTN002A</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>102683552.IB</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -12598,7 +12610,11 @@
           <t>26赣建工MTN001</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>102683554.IB</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -12779,7 +12795,11 @@
           <t>26冀中峰峰MTN002B</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>102683553.IB</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -13137,7 +13157,11 @@
           <t>26冀中峰峰MTN002A</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>102683552.IB</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -14619,7 +14643,9 @@
           <t>2.00 ~ 2.50</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr"/>
+      <c r="H14" s="2" t="n">
+        <v>2.34</v>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>安徽省交通控股集团有限公司</t>
